--- a/docs/StructureDefinition-br-core-observationbreastfeedingstatus.xlsx
+++ b/docs/StructureDefinition-br-core-observationbreastfeedingstatus.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T10:20:38-04:00</t>
+    <t>2026-09-10T12:27:48-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-br-core-observationbreastfeedingstatus.xlsx
+++ b/docs/StructureDefinition-br-core-observationbreastfeedingstatus.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T12:27:48-04:00</t>
+    <t>2026-09-10T13:05:34-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-br-core-observationbreastfeedingstatus.xlsx
+++ b/docs/StructureDefinition-br-core-observationbreastfeedingstatus.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>1.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:05:34-04:00</t>
+    <t>2026-09-10T13:58:29-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
